--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-05T16:04:06.152Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-05T16:26:52.044Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5065,7 +5065,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:04:07.035Z</t>
+    <t>2026-10-05T16:26:52.810Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -24442,7 +24442,7 @@
         <v>1318</v>
       </c>
       <c r="E2" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -24560,7 +24560,7 @@
         <v>1318</v>
       </c>
       <c r="E8" s="2">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -24578,7 +24578,7 @@
         <v>1318</v>
       </c>
       <c r="E9" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -24614,7 +24614,7 @@
         <v>1318</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -24650,7 +24650,7 @@
         <v>1318</v>
       </c>
       <c r="E13" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -24728,7 +24728,7 @@
         <v>1318</v>
       </c>
       <c r="E17" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -24746,7 +24746,7 @@
         <v>1318</v>
       </c>
       <c r="E18" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -24824,7 +24824,7 @@
         <v>1318</v>
       </c>
       <c r="E22" s="2">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -24862,7 +24862,7 @@
         <v>1318</v>
       </c>
       <c r="E24" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -24880,7 +24880,7 @@
         <v>1318</v>
       </c>
       <c r="E25" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -24898,7 +24898,7 @@
         <v>1318</v>
       </c>
       <c r="E26" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -24916,7 +24916,7 @@
         <v>1318</v>
       </c>
       <c r="E27" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -24934,7 +24934,7 @@
         <v>1318</v>
       </c>
       <c r="E28" s="2">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -24952,7 +24952,7 @@
         <v>1318</v>
       </c>
       <c r="E29" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -24970,7 +24970,7 @@
         <v>1318</v>
       </c>
       <c r="E30" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -24988,7 +24988,7 @@
         <v>1318</v>
       </c>
       <c r="E31" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -25006,7 +25006,7 @@
         <v>1318</v>
       </c>
       <c r="E32" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -25044,7 +25044,7 @@
         <v>1318</v>
       </c>
       <c r="E34" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -25062,7 +25062,7 @@
         <v>1318</v>
       </c>
       <c r="E35" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -25120,7 +25120,7 @@
         <v>1318</v>
       </c>
       <c r="E38" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -25158,7 +25158,7 @@
         <v>1318</v>
       </c>
       <c r="E40" s="2">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -25176,7 +25176,7 @@
         <v>1318</v>
       </c>
       <c r="E41" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -25274,7 +25274,7 @@
         <v>1318</v>
       </c>
       <c r="E46" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -25292,7 +25292,7 @@
         <v>1318</v>
       </c>
       <c r="E47" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -25310,7 +25310,7 @@
         <v>1318</v>
       </c>
       <c r="E48" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -25348,7 +25348,7 @@
         <v>1318</v>
       </c>
       <c r="E50" s="2">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -25366,7 +25366,7 @@
         <v>1318</v>
       </c>
       <c r="E51" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -25384,7 +25384,7 @@
         <v>1318</v>
       </c>
       <c r="E52" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -25520,7 +25520,7 @@
         <v>1318</v>
       </c>
       <c r="E59" s="2">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -25558,7 +25558,7 @@
         <v>1318</v>
       </c>
       <c r="E61" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -25656,7 +25656,7 @@
         <v>1318</v>
       </c>
       <c r="E66" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -25674,7 +25674,7 @@
         <v>1318</v>
       </c>
       <c r="E67" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -25692,7 +25692,7 @@
         <v>1318</v>
       </c>
       <c r="E68" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F68" s="2"/>
     </row>
@@ -25750,7 +25750,7 @@
         <v>1318</v>
       </c>
       <c r="E71" s="2">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -25768,7 +25768,7 @@
         <v>1318</v>
       </c>
       <c r="E72" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -25786,7 +25786,7 @@
         <v>1318</v>
       </c>
       <c r="E73" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F73" s="2"/>
     </row>
@@ -25824,7 +25824,7 @@
         <v>1318</v>
       </c>
       <c r="E75" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -25842,7 +25842,7 @@
         <v>1318</v>
       </c>
       <c r="E76" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -25860,7 +25860,7 @@
         <v>1318</v>
       </c>
       <c r="E77" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -25878,7 +25878,7 @@
         <v>1318</v>
       </c>
       <c r="E78" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F78" s="2"/>
     </row>
@@ -25936,7 +25936,7 @@
         <v>1318</v>
       </c>
       <c r="E81" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -25972,7 +25972,7 @@
         <v>1318</v>
       </c>
       <c r="E83" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -26050,7 +26050,7 @@
         <v>1318</v>
       </c>
       <c r="E87" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -26068,7 +26068,7 @@
         <v>1318</v>
       </c>
       <c r="E88" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -26086,7 +26086,7 @@
         <v>1318</v>
       </c>
       <c r="E89" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -26104,7 +26104,7 @@
         <v>1318</v>
       </c>
       <c r="E90" s="2">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -26122,7 +26122,7 @@
         <v>1318</v>
       </c>
       <c r="E91" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -26180,7 +26180,7 @@
         <v>1318</v>
       </c>
       <c r="E94" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -26218,7 +26218,7 @@
         <v>1318</v>
       </c>
       <c r="E96" s="2">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -26296,7 +26296,7 @@
         <v>1318</v>
       </c>
       <c r="E100" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -26414,7 +26414,7 @@
         <v>1318</v>
       </c>
       <c r="E106" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -26452,7 +26452,7 @@
         <v>1318</v>
       </c>
       <c r="E108" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -26630,7 +26630,7 @@
         <v>1318</v>
       </c>
       <c r="E117" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -26728,7 +26728,7 @@
         <v>1318</v>
       </c>
       <c r="E122" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -26746,7 +26746,7 @@
         <v>1318</v>
       </c>
       <c r="E123" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -26764,7 +26764,7 @@
         <v>1321</v>
       </c>
       <c r="E124" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -26818,7 +26818,7 @@
         <v>1321</v>
       </c>
       <c r="E127" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -26836,7 +26836,7 @@
         <v>1318</v>
       </c>
       <c r="E128" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -26854,7 +26854,7 @@
         <v>1318</v>
       </c>
       <c r="E129" s="2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -26872,7 +26872,7 @@
         <v>1318</v>
       </c>
       <c r="E130" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -26890,7 +26890,7 @@
         <v>1318</v>
       </c>
       <c r="E131" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -26908,7 +26908,7 @@
         <v>1318</v>
       </c>
       <c r="E132" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -26926,7 +26926,7 @@
         <v>1318</v>
       </c>
       <c r="E133" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -26944,7 +26944,7 @@
         <v>1318</v>
       </c>
       <c r="E134" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F134" s="2"/>
     </row>
@@ -26962,7 +26962,7 @@
         <v>1318</v>
       </c>
       <c r="E135" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -26980,7 +26980,7 @@
         <v>1321</v>
       </c>
       <c r="E136" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -27016,7 +27016,7 @@
         <v>1318</v>
       </c>
       <c r="E138" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F138" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -116,7 +116,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Regression (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 137 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 71 passed and 3 failed (pass rate 95.9%). 3 defect(s) were raised from real failures: DEF-004 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-005 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-006 9 rooms in one search are rejected: returns 200 instead of 400.</t>
+    <t>Hotel booking baseline · Regression (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 137 test cases are designed, 74 of them automated in 58 Playwright scripts. Execution ran 74 automated cases for real: 71 passed and 3 failed (pass rate 95.9%). 3 defect(s) were raised from real failures: DEF-004 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-005 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-006 9 rooms in one search are rejected: returns 200 instead of 400.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -149,7 +149,7 @@
     <t>jira-export</t>
   </si>
   <si>
-    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export): Jira REST API v3 JSON of AQPI-1, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+    <t>Jira export on GitHub (sri465inno/EQE-MVP-Neeraj@demo/jira-export): Jira REST API v3 JSON of AQPI-1, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
   </si>
   <si>
     <t>Jira epic</t>
@@ -158,19 +158,19 @@
     <t>AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27</t>
   </si>
   <si>
-    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export): Jira REST API v3 JSON of AQPI-2, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+    <t>Jira export on GitHub (sri465inno/EQE-MVP-Neeraj@demo/jira-export): Jira REST API v3 JSON of AQPI-2, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
   </si>
   <si>
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41)</t>
+    <t>sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-05T16:26:52.044Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41) at 2026-10-05T16:57:27.631Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5065,7 +5065,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:26:52.810Z</t>
+    <t>2026-10-05T16:57:28.413Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -24442,7 +24442,7 @@
         <v>1318</v>
       </c>
       <c r="E2" s="2">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -24560,7 +24560,7 @@
         <v>1318</v>
       </c>
       <c r="E8" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -24596,7 +24596,7 @@
         <v>1318</v>
       </c>
       <c r="E10" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -24614,7 +24614,7 @@
         <v>1318</v>
       </c>
       <c r="E11" s="2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -24632,7 +24632,7 @@
         <v>1318</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -24650,7 +24650,7 @@
         <v>1318</v>
       </c>
       <c r="E13" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -24728,7 +24728,7 @@
         <v>1318</v>
       </c>
       <c r="E17" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -24746,7 +24746,7 @@
         <v>1318</v>
       </c>
       <c r="E18" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -24824,7 +24824,7 @@
         <v>1318</v>
       </c>
       <c r="E22" s="2">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -24862,7 +24862,7 @@
         <v>1318</v>
       </c>
       <c r="E24" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -24880,7 +24880,7 @@
         <v>1318</v>
       </c>
       <c r="E25" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -24898,7 +24898,7 @@
         <v>1318</v>
       </c>
       <c r="E26" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -24934,7 +24934,7 @@
         <v>1318</v>
       </c>
       <c r="E28" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -24952,7 +24952,7 @@
         <v>1318</v>
       </c>
       <c r="E29" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -24970,7 +24970,7 @@
         <v>1318</v>
       </c>
       <c r="E30" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -25006,7 +25006,7 @@
         <v>1318</v>
       </c>
       <c r="E32" s="2">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -25044,7 +25044,7 @@
         <v>1318</v>
       </c>
       <c r="E34" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -25062,7 +25062,7 @@
         <v>1318</v>
       </c>
       <c r="E35" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -25120,7 +25120,7 @@
         <v>1318</v>
       </c>
       <c r="E38" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -25158,7 +25158,7 @@
         <v>1318</v>
       </c>
       <c r="E40" s="2">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -25176,7 +25176,7 @@
         <v>1318</v>
       </c>
       <c r="E41" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -25274,7 +25274,7 @@
         <v>1318</v>
       </c>
       <c r="E46" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -25292,7 +25292,7 @@
         <v>1318</v>
       </c>
       <c r="E47" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -25310,7 +25310,7 @@
         <v>1318</v>
       </c>
       <c r="E48" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -25348,7 +25348,7 @@
         <v>1318</v>
       </c>
       <c r="E50" s="2">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -25366,7 +25366,7 @@
         <v>1318</v>
       </c>
       <c r="E51" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -25384,7 +25384,7 @@
         <v>1318</v>
       </c>
       <c r="E52" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -25502,7 +25502,7 @@
         <v>1318</v>
       </c>
       <c r="E58" s="2">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -25520,7 +25520,7 @@
         <v>1318</v>
       </c>
       <c r="E59" s="2">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -25558,7 +25558,7 @@
         <v>1318</v>
       </c>
       <c r="E61" s="2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -25656,7 +25656,7 @@
         <v>1318</v>
       </c>
       <c r="E66" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -25674,7 +25674,7 @@
         <v>1318</v>
       </c>
       <c r="E67" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -25692,7 +25692,7 @@
         <v>1318</v>
       </c>
       <c r="E68" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F68" s="2"/>
     </row>
@@ -25750,7 +25750,7 @@
         <v>1318</v>
       </c>
       <c r="E71" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -25768,7 +25768,7 @@
         <v>1318</v>
       </c>
       <c r="E72" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -25786,7 +25786,7 @@
         <v>1318</v>
       </c>
       <c r="E73" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F73" s="2"/>
     </row>
@@ -25824,7 +25824,7 @@
         <v>1318</v>
       </c>
       <c r="E75" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -25842,7 +25842,7 @@
         <v>1318</v>
       </c>
       <c r="E76" s="2">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -25878,7 +25878,7 @@
         <v>1318</v>
       </c>
       <c r="E78" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F78" s="2"/>
     </row>
@@ -25936,7 +25936,7 @@
         <v>1318</v>
       </c>
       <c r="E81" s="2">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -25954,7 +25954,7 @@
         <v>1318</v>
       </c>
       <c r="E82" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -26050,7 +26050,7 @@
         <v>1318</v>
       </c>
       <c r="E87" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -26086,7 +26086,7 @@
         <v>1318</v>
       </c>
       <c r="E89" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -26104,7 +26104,7 @@
         <v>1318</v>
       </c>
       <c r="E90" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -26122,7 +26122,7 @@
         <v>1318</v>
       </c>
       <c r="E91" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -26180,7 +26180,7 @@
         <v>1318</v>
       </c>
       <c r="E94" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -26218,7 +26218,7 @@
         <v>1318</v>
       </c>
       <c r="E96" s="2">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -26296,7 +26296,7 @@
         <v>1318</v>
       </c>
       <c r="E100" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -26414,7 +26414,7 @@
         <v>1318</v>
       </c>
       <c r="E106" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -26630,7 +26630,7 @@
         <v>1318</v>
       </c>
       <c r="E117" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -26728,7 +26728,7 @@
         <v>1318</v>
       </c>
       <c r="E122" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -26746,7 +26746,7 @@
         <v>1318</v>
       </c>
       <c r="E123" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -26764,7 +26764,7 @@
         <v>1321</v>
       </c>
       <c r="E124" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -26782,7 +26782,7 @@
         <v>1318</v>
       </c>
       <c r="E125" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -26800,7 +26800,7 @@
         <v>1318</v>
       </c>
       <c r="E126" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -26818,7 +26818,7 @@
         <v>1321</v>
       </c>
       <c r="E127" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -26836,7 +26836,7 @@
         <v>1318</v>
       </c>
       <c r="E128" s="2">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -26854,7 +26854,7 @@
         <v>1318</v>
       </c>
       <c r="E129" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -26890,7 +26890,7 @@
         <v>1318</v>
       </c>
       <c r="E131" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -26908,7 +26908,7 @@
         <v>1318</v>
       </c>
       <c r="E132" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -26962,7 +26962,7 @@
         <v>1318</v>
       </c>
       <c r="E135" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -26980,7 +26980,7 @@
         <v>1321</v>
       </c>
       <c r="E136" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -26998,7 +26998,7 @@
         <v>1318</v>
       </c>
       <c r="E137" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F137" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41) at 2026-10-05T16:57:27.631Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/EQE-MVP-Neeraj@demo/hotel-booking-platform (452df41) at 2026-10-05T17:10:31.196Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5065,7 +5065,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:57:28.413Z</t>
+    <t>2026-10-05T17:10:31.996Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -24442,7 +24442,7 @@
         <v>1318</v>
       </c>
       <c r="E2" s="2">
-        <v>497</v>
+        <v>540</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -24560,7 +24560,7 @@
         <v>1318</v>
       </c>
       <c r="E8" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -24578,7 +24578,7 @@
         <v>1318</v>
       </c>
       <c r="E9" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -24596,7 +24596,7 @@
         <v>1318</v>
       </c>
       <c r="E10" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -24614,7 +24614,7 @@
         <v>1318</v>
       </c>
       <c r="E11" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -24632,7 +24632,7 @@
         <v>1318</v>
       </c>
       <c r="E12" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -24728,7 +24728,7 @@
         <v>1318</v>
       </c>
       <c r="E17" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -24746,7 +24746,7 @@
         <v>1318</v>
       </c>
       <c r="E18" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -24824,7 +24824,7 @@
         <v>1318</v>
       </c>
       <c r="E22" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -24862,7 +24862,7 @@
         <v>1318</v>
       </c>
       <c r="E24" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -24898,7 +24898,7 @@
         <v>1318</v>
       </c>
       <c r="E26" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -24916,7 +24916,7 @@
         <v>1318</v>
       </c>
       <c r="E27" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -24934,7 +24934,7 @@
         <v>1318</v>
       </c>
       <c r="E28" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -24952,7 +24952,7 @@
         <v>1318</v>
       </c>
       <c r="E29" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -24970,7 +24970,7 @@
         <v>1318</v>
       </c>
       <c r="E30" s="2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -25006,7 +25006,7 @@
         <v>1318</v>
       </c>
       <c r="E32" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F32" s="2"/>
     </row>
@@ -25044,7 +25044,7 @@
         <v>1318</v>
       </c>
       <c r="E34" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -25062,7 +25062,7 @@
         <v>1318</v>
       </c>
       <c r="E35" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -25120,7 +25120,7 @@
         <v>1318</v>
       </c>
       <c r="E38" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -25158,7 +25158,7 @@
         <v>1318</v>
       </c>
       <c r="E40" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -25176,7 +25176,7 @@
         <v>1318</v>
       </c>
       <c r="E41" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F41" s="2"/>
     </row>
@@ -25274,7 +25274,7 @@
         <v>1318</v>
       </c>
       <c r="E46" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -25292,7 +25292,7 @@
         <v>1318</v>
       </c>
       <c r="E47" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -25310,7 +25310,7 @@
         <v>1318</v>
       </c>
       <c r="E48" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F48" s="2"/>
     </row>
@@ -25348,7 +25348,7 @@
         <v>1318</v>
       </c>
       <c r="E50" s="2">
-        <v>224</v>
+        <v>287</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -25366,7 +25366,7 @@
         <v>1318</v>
       </c>
       <c r="E51" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -25384,7 +25384,7 @@
         <v>1318</v>
       </c>
       <c r="E52" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F52" s="2"/>
     </row>
@@ -25502,7 +25502,7 @@
         <v>1318</v>
       </c>
       <c r="E58" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -25520,7 +25520,7 @@
         <v>1318</v>
       </c>
       <c r="E59" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F59" s="2"/>
     </row>
@@ -25558,7 +25558,7 @@
         <v>1318</v>
       </c>
       <c r="E61" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F61" s="2"/>
     </row>
@@ -25656,7 +25656,7 @@
         <v>1318</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -25674,7 +25674,7 @@
         <v>1318</v>
       </c>
       <c r="E67" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -25750,7 +25750,7 @@
         <v>1318</v>
       </c>
       <c r="E71" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -25768,7 +25768,7 @@
         <v>1318</v>
       </c>
       <c r="E72" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -25786,7 +25786,7 @@
         <v>1318</v>
       </c>
       <c r="E73" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" s="2"/>
     </row>
@@ -25824,7 +25824,7 @@
         <v>1318</v>
       </c>
       <c r="E75" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -25842,7 +25842,7 @@
         <v>1318</v>
       </c>
       <c r="E76" s="2">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -25860,7 +25860,7 @@
         <v>1318</v>
       </c>
       <c r="E77" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -25878,7 +25878,7 @@
         <v>1318</v>
       </c>
       <c r="E78" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F78" s="2"/>
     </row>
@@ -25936,7 +25936,7 @@
         <v>1318</v>
       </c>
       <c r="E81" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -25954,7 +25954,7 @@
         <v>1318</v>
       </c>
       <c r="E82" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -25972,7 +25972,7 @@
         <v>1318</v>
       </c>
       <c r="E83" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -26050,7 +26050,7 @@
         <v>1318</v>
       </c>
       <c r="E87" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -26068,7 +26068,7 @@
         <v>1318</v>
       </c>
       <c r="E88" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -26086,7 +26086,7 @@
         <v>1318</v>
       </c>
       <c r="E89" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -26104,7 +26104,7 @@
         <v>1318</v>
       </c>
       <c r="E90" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -26122,7 +26122,7 @@
         <v>1318</v>
       </c>
       <c r="E91" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F91" s="2"/>
     </row>
@@ -26180,7 +26180,7 @@
         <v>1318</v>
       </c>
       <c r="E94" s="2">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -26218,7 +26218,7 @@
         <v>1318</v>
       </c>
       <c r="E96" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="F96" s="2"/>
     </row>
@@ -26296,7 +26296,7 @@
         <v>1318</v>
       </c>
       <c r="E100" s="2">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F100" s="2"/>
     </row>
@@ -26414,7 +26414,7 @@
         <v>1318</v>
       </c>
       <c r="E106" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F106" s="2"/>
     </row>
@@ -26452,7 +26452,7 @@
         <v>1318</v>
       </c>
       <c r="E108" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F108" s="2"/>
     </row>
@@ -26630,7 +26630,7 @@
         <v>1318</v>
       </c>
       <c r="E117" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F117" s="2"/>
     </row>
@@ -26728,7 +26728,7 @@
         <v>1318</v>
       </c>
       <c r="E122" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -26746,7 +26746,7 @@
         <v>1318</v>
       </c>
       <c r="E123" s="2">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -26764,7 +26764,7 @@
         <v>1321</v>
       </c>
       <c r="E124" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -26782,7 +26782,7 @@
         <v>1318</v>
       </c>
       <c r="E125" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -26800,7 +26800,7 @@
         <v>1318</v>
       </c>
       <c r="E126" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -26818,7 +26818,7 @@
         <v>1321</v>
       </c>
       <c r="E127" s="2">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -26836,7 +26836,7 @@
         <v>1318</v>
       </c>
       <c r="E128" s="2">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -26854,7 +26854,7 @@
         <v>1318</v>
       </c>
       <c r="E129" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -26872,7 +26872,7 @@
         <v>1318</v>
       </c>
       <c r="E130" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -26890,7 +26890,7 @@
         <v>1318</v>
       </c>
       <c r="E131" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F131" s="2"/>
     </row>
@@ -26908,7 +26908,7 @@
         <v>1318</v>
       </c>
       <c r="E132" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -26944,7 +26944,7 @@
         <v>1318</v>
       </c>
       <c r="E134" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F134" s="2"/>
     </row>
@@ -26962,7 +26962,7 @@
         <v>1318</v>
       </c>
       <c r="E135" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F135" s="2"/>
     </row>
@@ -26980,7 +26980,7 @@
         <v>1321</v>
       </c>
       <c r="E136" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -26998,7 +26998,7 @@
         <v>1318</v>
       </c>
       <c r="E137" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F137" s="2"/>
     </row>
@@ -27016,7 +27016,7 @@
         <v>1318</v>
       </c>
       <c r="E138" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F138" s="2"/>
     </row>
